--- a/BADesign/Excel/BossMonster.xlsx
+++ b/BADesign/Excel/BossMonster.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="32">
   <si>
     <t>Client</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t>기본공격</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Enemy/1stBoss/AM_1stBossSlashBackSpin.AM_1stBossSlashBackSpin</t>
   </si>
   <si>
     <t>기본공격 (10000 = 100%)
@@ -71,18 +74,31 @@
 Var1 확률/체력, Var2 거리/범위, Var3 횟수/기타</t>
   </si>
   <si>
-    <t>패턴공격1번</t>
-  </si>
-  <si>
-    <t>Var1 : 발동 확률(3000 = 30%)
- Var2 : 내 체력 Var2% 이하</t>
-  </si>
-  <si>
-    <t>패턴공격2번</t>
+    <t>3회</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Enemy/1stBoss/AM_1stBossSlashSwingBackspin.AM_1stBossSlashSwingBackspin</t>
+  </si>
+  <si>
+    <t>Var1 : 발동 확률 (5000 = 50%)
+Var2 : 플레이어와의 거리 (2M 이상)
+Var3 : 연속 타격 횟수 (N회)</t>
+  </si>
+  <si>
+    <t>찌르기</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Enemy/1stBoss/AM_1stBossLeftStab.AM_1stBossLeftStab</t>
   </si>
   <si>
     <t>Var1 : 발동 확률 ( 2000 = 20%)
  Var2 : 플레이어와의 거리 Var2M 이상</t>
+  </si>
+  <si>
+    <t>5콤보</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Enemy/1stBoss/AM_1stBossChargedCombo.AM_1stBossChargedCombo</t>
   </si>
   <si>
     <t>회피 패턴</t>
@@ -91,6 +107,16 @@
     <t>Var1 : 발동 확률 ( 2000 = 20%)
  Var2 : 플레이어와의 거리 Var2M 이하
  Var3 : 연속 타격횟수 Var3 이상</t>
+  </si>
+  <si>
+    <t>패턴공격1번</t>
+  </si>
+  <si>
+    <t>Var1 : 발동 확률(3000 = 30%)
+ Var2 : 내 체력 Var2% 이하</t>
+  </si>
+  <si>
+    <t>패턴공격2번</t>
   </si>
 </sst>
 </file>
@@ -418,7 +444,16 @@
   <cols>
     <col customWidth="1" min="2" max="2" width="3.5"/>
     <col customWidth="1" min="3" max="3" width="8.75"/>
-    <col customWidth="1" min="7" max="7" width="25.13"/>
+    <col customWidth="1" min="4" max="4" width="66.75"/>
+    <col customWidth="1" min="5" max="5" width="7.38"/>
+    <col customWidth="1" min="6" max="6" width="10.63"/>
+    <col customWidth="1" min="7" max="7" width="30.88"/>
+    <col customWidth="1" min="8" max="8" width="5.13"/>
+    <col customWidth="1" min="9" max="10" width="4.0"/>
+    <col customWidth="1" min="12" max="12" width="9.5"/>
+    <col customWidth="1" min="13" max="13" width="9.88"/>
+    <col customWidth="1" min="14" max="14" width="12.0"/>
+    <col customWidth="1" min="15" max="15" width="12.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -523,7 +558,9 @@
       <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="E3" s="2">
         <v>2.0</v>
       </c>
@@ -531,7 +568,7 @@
         <v>1.0</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" s="8">
         <v>10000.0</v>
@@ -560,9 +597,11 @@
         <v>101.0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="E4" s="2">
         <v>3.0</v>
       </c>
@@ -570,10 +609,10 @@
         <v>2.0</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H4" s="8">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="I4" s="2">
         <v>80.0</v>
@@ -601,9 +640,11 @@
         <v>102.0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="E5" s="2">
         <v>7.0</v>
       </c>
@@ -611,10 +652,10 @@
         <v>3.0</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H5" s="8">
-        <v>2000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="I5" s="2">
         <v>20.0</v>
@@ -642,43 +683,86 @@
         <v>103.0</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="E6" s="2">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="F6" s="2">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6" s="8">
         <v>2000.0</v>
       </c>
       <c r="I6" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="J6" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="J6" s="6"/>
+      <c r="K6" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="2">
+        <v>800.0</v>
+      </c>
+      <c r="M6" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="N6" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="O6" s="2">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6"/>
+      <c r="B7" s="2">
+        <v>104.0</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="8">
+        <v>2000.0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="J7" s="2">
         <v>5.0</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K7" s="2">
         <v>2.0</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L7" s="2">
         <v>1200.0</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M7" s="2">
         <v>180.0</v>
       </c>
-      <c r="N6" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="O6" s="6"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="9"/>
+      <c r="N7" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="O7" s="6"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="9"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -815,7 +899,7 @@
         <v>1.0</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" s="8">
         <v>10000.0</v>
@@ -844,7 +928,7 @@
         <v>201.0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2">
@@ -854,7 +938,7 @@
         <v>2.0</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H4" s="8">
         <v>3000.0</v>
@@ -885,7 +969,7 @@
         <v>202.0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2">
@@ -895,7 +979,7 @@
         <v>3.0</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H5" s="8">
         <v>2000.0</v>
@@ -926,7 +1010,7 @@
         <v>203.0</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="2">
@@ -936,7 +1020,7 @@
         <v>4.0</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H6" s="8">
         <v>2000.0</v>
@@ -1090,7 +1174,7 @@
         <v>1.0</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" s="8">
         <v>10000.0</v>
@@ -1119,7 +1203,7 @@
         <v>301.0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2">
@@ -1129,7 +1213,7 @@
         <v>2.0</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H4" s="8">
         <v>3000.0</v>
@@ -1160,7 +1244,7 @@
         <v>302.0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2">
@@ -1170,7 +1254,7 @@
         <v>3.0</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H5" s="8">
         <v>2000.0</v>
@@ -1201,7 +1285,7 @@
         <v>303.0</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="2">
@@ -1211,7 +1295,7 @@
         <v>4.0</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H6" s="8">
         <v>2000.0</v>

--- a/BADesign/Excel/BossMonster.xlsx
+++ b/BADesign/Excel/BossMonster.xlsx
@@ -665,7 +665,7 @@
         <v>1.5</v>
       </c>
       <c r="L5" s="2">
-        <v>800.0</v>
+        <v>300.0</v>
       </c>
       <c r="M5" s="2">
         <v>15.0</v>
@@ -708,7 +708,7 @@
         <v>1.5</v>
       </c>
       <c r="L6" s="2">
-        <v>800.0</v>
+        <v>280.0</v>
       </c>
       <c r="M6" s="2">
         <v>15.0</v>
@@ -751,7 +751,7 @@
         <v>2.0</v>
       </c>
       <c r="L7" s="2">
-        <v>1200.0</v>
+        <v>1000.0</v>
       </c>
       <c r="M7" s="2">
         <v>180.0</v>

--- a/BADesign/Excel/BossMonster.xlsx
+++ b/BADesign/Excel/BossMonster.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="1StageBossAttack" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="36">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -81,25 +81,112 @@
     <t xml:space="preserve">NextComboTid</t>
   </si>
   <si>
-    <t xml:space="preserve">ComboTransitionTIme</t>
+    <t xml:space="preserve">ComboTransitionTime</t>
   </si>
   <si>
     <t xml:space="preserve">기본공격</t>
   </si>
   <si>
-    <t xml:space="preserve">/Game/Assets/Enemy/1stBoss/AM_1stBossSlashBackSpin.AM_1stBossNormal</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Game/Assets/Enemy/1stBoss/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">AM_1stBossNormal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.AM_1stBossNormal</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">3회</t>
   </si>
   <si>
-    <t xml:space="preserve">/Game/Assets/Enemy/1stBoss/AM_1stBossSlashSwingBackspin.AM_1stBossComboTrace</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Game/Assets/Enemy/1stBoss/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">.AM_1stBossComboTrace</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.AM_1stBossComboTrace</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">찌르기</t>
   </si>
   <si>
-    <t xml:space="preserve">/Game/Assets/Enemy/1stBoss/AM_1stBossLeftStab.AM_1stBossDash</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Game/Assets/Enemy/1stBoss/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">AM_1stBossDash</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.AM_1stBossDash</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">차징</t>
@@ -111,73 +198,54 @@
     <t xml:space="preserve">차징 광역</t>
   </si>
   <si>
-    <t xml:space="preserve">/Game/Assets/Enemy/1stBoss/AM_1stBossChargedCombo.AM_1stBossChargedArea</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Game/Assets/Enemy/1stBoss/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">AM_1stBossChargedArea</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.AM_1stBossChargedArea</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">패링 패턴</t>
   </si>
   <si>
-    <t xml:space="preserve">/Game/Assets/Enemy/1stBoss/AM_1stBossChargedCombo.AM_1stBossParried</t>
+    <t xml:space="preserve">/Game/Assets/Enemy/1stBoss/AM_1stBossParried.AM_1stBossParried</t>
   </si>
   <si>
     <t xml:space="preserve">후방 대응</t>
   </si>
   <si>
-    <t xml:space="preserve">/Game/Assets/Enemy/1stBoss/AM_1stBossChargedCombo.AM_1stBossBackNormal</t>
+    <t xml:space="preserve">/Game/Assets/Enemy/1stBoss/AM_1stBossBackNormal.AM_1stBossBackNormal</t>
   </si>
   <si>
     <t xml:space="preserve">측면 대응</t>
   </si>
   <si>
-    <t xml:space="preserve">/Game/Assets/Enemy/1stBoss/AM_1stBossChargedCombo.AM_1stBossSideNormal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ConditionType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Var1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Var2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Var3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackAngle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기본공격 (10000 = 100%)
-(발동확률을 제외헀을때 패턴)
-Var1 확률/체력, Var2 거리/범위, Var3 횟수/기타</t>
-  </si>
-  <si>
-    <t xml:space="preserve">패턴공격1번</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Var1 : 발동 확률(3000 = 30%)
- Var2 : 내 체력 Var2% 이하</t>
-  </si>
-  <si>
-    <t xml:space="preserve">패턴공격2번</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Var1 : 발동 확률 ( 2000 = 20%)
- Var2 : 플레이어와의 거리 Var2M 이상</t>
-  </si>
-  <si>
-    <t xml:space="preserve">회피 패턴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Var1 : 발동 확률 ( 2000 = 20%)
- Var2 : 플레이어와의 거리 Var2M 이하
- Var3 : 연속 타격횟수 Var3 이상</t>
+    <t xml:space="preserve">/Game/Assets/Enemy/1stBoss/AM_1stBossSideNormal.AM_1stBossSideNormal</t>
   </si>
 </sst>
 </file>
@@ -318,7 +386,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -361,26 +429,6 @@
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1247,7 +1295,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="3.2"/>
@@ -1283,7 +1331,7 @@
         <v>1</v>
       </c>
       <c r="G1" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1" s="2" t="n">
         <v>1</v>
@@ -1307,6 +1355,18 @@
         <v>1</v>
       </c>
       <c r="O1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1314,210 +1374,516 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="L2" s="13" t="s">
+      <c r="P2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="3" t="s">
+      <c r="Q2" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3"/>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="P4" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="15" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="3" t="n">
+      <c r="Q4" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>600</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3"/>
+      <c r="B7" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="P9" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="M3" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3" t="n">
-        <v>201</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="15" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O5" s="3" t="n">
+      <c r="Q9" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3"/>
+      <c r="B10" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P10" s="4" t="n">
         <v>150</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3" t="n">
-        <v>203</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" s="3"/>
+      <c r="Q10" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1536,7 +1902,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="3.2"/>
@@ -1566,7 +1932,7 @@
         <v>1</v>
       </c>
       <c r="G1" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1" s="2" t="n">
         <v>1</v>
@@ -1590,6 +1956,18 @@
         <v>1</v>
       </c>
       <c r="O1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1597,210 +1975,516 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="L2" s="13" t="s">
+      <c r="P2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="3" t="s">
+      <c r="Q2" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3"/>
-      <c r="B3" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="15" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="3" t="n">
+      <c r="D3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="M3" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" s="3" t="n">
+      <c r="Q3" s="4" t="n">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
-      <c r="B4" s="3" t="n">
-        <v>301</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3" t="n">
+      <c r="B4" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="15" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L4" s="3" t="n">
+      <c r="O4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="P4" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="Q4" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>100</v>
+      <c r="R4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3"/>
-      <c r="B5" s="3" t="n">
-        <v>302</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3" t="n">
+      <c r="B5" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N5" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>150</v>
+      <c r="O5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>600</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3"/>
-      <c r="B6" s="3" t="n">
-        <v>303</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3" t="n">
+      <c r="B6" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3"/>
+      <c r="B7" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" s="3"/>
+      <c r="O8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3"/>
+      <c r="B10" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/BADesign/Excel/BossMonster.xlsx
+++ b/BADesign/Excel/BossMonster.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="37">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t xml:space="preserve">/Game/Assets/Enemy/1stBoss/AM_1stBossSideNormal.AM_1stBossSideNormal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Assets/Enemy/1stBoss/AM_1stBossComboTrace.AM_1stBossComboTrace</t>
   </si>
 </sst>
 </file>
@@ -1910,6 +1913,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="23.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="11.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="56.94"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2129,7 +2133,7 @@
         <v>3</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="P4" s="4" t="n">
         <v>200</v>

--- a/BADesign/Excel/BossMonster.xlsx
+++ b/BADesign/Excel/BossMonster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.293.56114"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="480" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="460" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="1StageBossAttack" sheetId="1" r:id="rId1"/>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="T6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U6" s="3">
         <v>1</v>
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H7" s="3">
         <v>0</v>
@@ -1584,7 +1584,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="3">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="N7" s="3">
         <v>25</v>
@@ -1674,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="T8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U8" s="3">
         <v>450</v>

--- a/BADesign/Excel/BossMonster.xlsx
+++ b/BADesign/Excel/BossMonster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.293.56114"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="460" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="450" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="1StageBossAttack" sheetId="1" r:id="rId1"/>
@@ -1319,10 +1319,10 @@
         <v>24</v>
       </c>
       <c r="P3" s="3">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="Q3" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R3" s="3">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         <v>26</v>
       </c>
       <c r="P4" s="3">
-        <v>200</v>
+        <v>330</v>
       </c>
       <c r="Q4" s="3">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="R4" s="3">
         <v>0</v>
@@ -1526,10 +1526,10 @@
         <v>30</v>
       </c>
       <c r="P6" s="3">
-        <v>220</v>
+        <v>320</v>
       </c>
       <c r="Q6" s="3">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3">
@@ -1593,10 +1593,10 @@
         <v>32</v>
       </c>
       <c r="P7" s="3">
-        <v>300</v>
+        <v>9999</v>
       </c>
       <c r="Q7" s="3">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="R7" s="3">
         <v>108</v>
@@ -1665,7 +1665,7 @@
         <v>250</v>
       </c>
       <c r="Q8" s="3">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
@@ -1731,10 +1731,10 @@
         <v>36</v>
       </c>
       <c r="P9" s="3">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="Q9" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R9" s="3">
         <v>0</v>
@@ -1800,10 +1800,10 @@
         <v>38</v>
       </c>
       <c r="P10" s="3">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="Q10" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R10" s="3">
         <v>0</v>
@@ -1872,7 +1872,7 @@
         <v>9999</v>
       </c>
       <c r="Q11" s="3">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="R11" s="3">
         <v>0</v>
